--- a/exports/HCLTECH_full_report.xlsx
+++ b/exports/HCLTECH_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44575.55208333334</v>
+        <v>44578.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1332</v>
+        <v>1260.6</v>
       </c>
       <c r="I2" t="n">
         <v>1287.77449884</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.07</v>
+        <v>-2.46</v>
       </c>
       <c r="L2" t="n">
-        <v>0.96</v>
+        <v>3.78</v>
       </c>
       <c r="M2" t="n">
-        <v>0.63</v>
+        <v>4.43</v>
       </c>
       <c r="N2" t="n">
-        <v>1.59</v>
+        <v>5.36</v>
       </c>
       <c r="O2" t="n">
         <v>0.08</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.12</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1134.8</v>
+        <v>1169.7</v>
       </c>
       <c r="I3" t="n">
         <v>1162.334053580946</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>9.98</v>
+        <v>7.21</v>
       </c>
       <c r="L3" t="n">
         <v>0.98</v>
@@ -612,7 +647,7 @@
         <v>1.83</v>
       </c>
       <c r="N3" t="n">
-        <v>3.19</v>
+        <v>3.32</v>
       </c>
       <c r="O3" t="n">
         <v>-5.36</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1151</v>
+        <v>1102.4</v>
       </c>
       <c r="I4" t="n">
         <v>1131.535946426321</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.6</v>
+        <v>-5.75</v>
       </c>
       <c r="L4" t="n">
-        <v>3.22</v>
+        <v>6.34</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>3.91</v>
       </c>
       <c r="N4" t="n">
-        <v>2.37</v>
+        <v>4.52</v>
       </c>
       <c r="O4" t="n">
         <v>3.32</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>6.31</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44627.55208333334</v>
+        <v>44628.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1153.75</v>
+        <v>1172</v>
       </c>
       <c r="I5" t="n">
         <v>1156.480982050224</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.66</v>
+        <v>-6.31</v>
       </c>
       <c r="L5" t="n">
-        <v>5.34</v>
+        <v>6.94</v>
       </c>
       <c r="M5" t="n">
         <v>1.51</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>6.26</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44659.55208333334</v>
+        <v>44662.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1166.3</v>
+        <v>1134.75</v>
       </c>
       <c r="I6" t="n">
         <v>1153.349277009912</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.49</v>
+        <v>-3.18</v>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>3.41</v>
       </c>
       <c r="M6" t="n">
         <v>0.89</v>
       </c>
       <c r="N6" t="n">
-        <v>2.33</v>
+        <v>2.73</v>
       </c>
       <c r="O6" t="n">
         <v>1.66</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.66</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1006.5</v>
+        <v>1041.75</v>
       </c>
       <c r="I7" t="n">
         <v>1030.547730258504</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K7" t="n">
-        <v>11.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>2.58</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>6.8</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1019.9</v>
+        <v>987.05</v>
       </c>
       <c r="I8" t="n">
         <v>997.1302205758714</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.1</v>
+        <v>-5.25</v>
       </c>
       <c r="L8" t="n">
-        <v>3.24</v>
+        <v>5.33</v>
       </c>
       <c r="M8" t="n">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="N8" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
         <v>3.53</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.36</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44769.55208333334</v>
+        <v>44770.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>928.5</v>
+        <v>945.15</v>
       </c>
       <c r="I9" t="n">
         <v>930.1145301492724</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K9" t="n">
-        <v>5.93</v>
+        <v>4.24</v>
       </c>
       <c r="L9" t="n">
         <v>2.02</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>4.73</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>961</v>
+        <v>944.1</v>
       </c>
       <c r="I10" t="n">
         <v>945.2571939913041</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>1.68</v>
+        <v>-0.11</v>
       </c>
       <c r="L10" t="n">
         <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0.28</v>
+        <v>1.15</v>
       </c>
       <c r="N10" t="n">
         <v>1.43</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>4.08</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>950.1</v>
+        <v>959.2</v>
       </c>
       <c r="I11" t="n">
         <v>952.2610208732434</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.64</v>
+        <v>-1.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
         <v>0.82</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>3.74</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44818.55208333334</v>
+        <v>44819.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>932.6</v>
+        <v>922</v>
       </c>
       <c r="I12" t="n">
         <v>924.4136126628258</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.77</v>
+        <v>-3.88</v>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
         <v>2.31</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.63</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44834.38541666666</v>
+        <v>44834.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>926.45</v>
+        <v>932.95</v>
       </c>
       <c r="I13" t="n">
         <v>932.494345393503</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.48</v>
+        <v>-1.19</v>
       </c>
       <c r="L13" t="n">
         <v>1.59</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>4.3</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1100</v>
+        <v>1026.05</v>
       </c>
       <c r="I14" t="n">
         <v>1098.159950857628</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>69</v>
+        <v>69.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>17.91</v>
+        <v>9.98</v>
       </c>
       <c r="L14" t="n">
         <v>1.82</v>
       </c>
       <c r="M14" t="n">
-        <v>1.37</v>
+        <v>2.27</v>
       </c>
       <c r="N14" t="n">
-        <v>1.93</v>
+        <v>6.43</v>
       </c>
       <c r="O14" t="n">
         <v>1.09</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>7.9</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44932.55208333334</v>
+        <v>44935.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1033</v>
+        <v>1063</v>
       </c>
       <c r="I15" t="n">
         <v>1062.298261593048</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.68</v>
+        <v>-3.6</v>
       </c>
       <c r="L15" t="n">
         <v>4.77</v>
       </c>
       <c r="M15" t="n">
-        <v>0.72</v>
+        <v>1.16</v>
       </c>
       <c r="N15" t="n">
-        <v>1.39</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
         <v>-6.43</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.63</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44978.38541666666</v>
+        <v>44978.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>1112.5</v>
+        <v>1105</v>
       </c>
       <c r="I16" t="n">
         <v>1106.517512901906</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K16" t="n">
-        <v>4.66</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>2.16</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>4.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1119.9</v>
+        <v>1125.65</v>
       </c>
       <c r="I17" t="n">
         <v>1123.257939579916</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.35</v>
+        <v>-1.87</v>
       </c>
       <c r="L17" t="n">
-        <v>2.22</v>
+        <v>3.89</v>
       </c>
       <c r="M17" t="n">
         <v>0.99</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>3.63</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1100.95</v>
+        <v>1075.2</v>
       </c>
       <c r="I18" t="n">
         <v>1084.789317413539</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.19</v>
+        <v>-4.48</v>
       </c>
       <c r="L18" t="n">
-        <v>2.72</v>
+        <v>4.58</v>
       </c>
       <c r="M18" t="n">
         <v>1.42</v>
       </c>
       <c r="N18" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="O18" t="n">
         <v>0.72</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.7</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>1090.9</v>
+        <v>1098.4</v>
       </c>
       <c r="I19" t="n">
         <v>1097.149339274209</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.46</v>
+        <v>-2.16</v>
       </c>
       <c r="L19" t="n">
         <v>3.89</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>4.59</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1072.5</v>
+        <v>1035.4</v>
       </c>
       <c r="I20" t="n">
         <v>1057.235466927538</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>10</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.36</v>
+        <v>-5.74</v>
       </c>
       <c r="L20" t="n">
-        <v>3.22</v>
+        <v>7.47</v>
       </c>
       <c r="M20" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O20" t="n">
         <v>1.19</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>5.55</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45056.55208333334</v>
+        <v>45057.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1079</v>
+        <v>1091.1</v>
       </c>
       <c r="I21" t="n">
         <v>1087.890818957814</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.21</v>
+        <v>-5.38</v>
       </c>
       <c r="L21" t="n">
-        <v>5.16</v>
+        <v>5.52</v>
       </c>
       <c r="M21" t="n">
         <v>1.64</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.57</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45114.38541666666</v>
+        <v>45114.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>1167.85</v>
+        <v>1157.95</v>
       </c>
       <c r="I22" t="n">
         <v>1158.017209820003</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>7.03</v>
+        <v>6.13</v>
       </c>
       <c r="L22" t="n">
         <v>2.6</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.07</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45124.55208333334</v>
+        <v>45125.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1155.1</v>
+        <v>1162.45</v>
       </c>
       <c r="I23" t="n">
         <v>1158.570283828785</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>0.25</v>
+        <v>-0.39</v>
       </c>
       <c r="L23" t="n">
         <v>1.24</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45131.38541666666</v>
+        <v>45131.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>1119.8</v>
+        <v>1111.6</v>
       </c>
       <c r="I24" t="n">
         <v>1113.769066263153</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.67</v>
+        <v>-4.37</v>
       </c>
       <c r="L24" t="n">
         <v>5.8</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>5.4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45141.55208333334</v>
+        <v>45142.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1123.4</v>
+        <v>1148.25</v>
       </c>
       <c r="I25" t="n">
         <v>1143.420204342523</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.06</v>
+        <v>-3.3</v>
       </c>
       <c r="L25" t="n">
-        <v>2.73</v>
+        <v>3.67</v>
       </c>
       <c r="M25" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="N25" t="n">
         <v>2.11</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.9</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45194.55208333334</v>
+        <v>45195.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1266.05</v>
+        <v>1259.5</v>
       </c>
       <c r="I26" t="n">
         <v>1263.457297483325</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K26" t="n">
-        <v>10.26</v>
+        <v>9.69</v>
       </c>
       <c r="L26" t="n">
         <v>2.02</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>3.93</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45215.55208333334</v>
+        <v>45216.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1272</v>
+        <v>1277.25</v>
       </c>
       <c r="I27" t="n">
         <v>1274.66595711925</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.99</v>
+        <v>-1.41</v>
       </c>
       <c r="L27" t="n">
         <v>1.57</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.52</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.55208333334</v>
+        <v>45281.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1437.95</v>
+        <v>1432.75</v>
       </c>
       <c r="I28" t="n">
         <v>1435.94078085482</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>64.16666666666667</v>
+        <v>65</v>
       </c>
       <c r="K28" t="n">
-        <v>12.58</v>
+        <v>12.17</v>
       </c>
       <c r="L28" t="n">
         <v>5.1</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.32</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45300.55208333334</v>
+        <v>45301.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1468.75</v>
+        <v>1489.95</v>
       </c>
       <c r="I29" t="n">
         <v>1479.270138000418</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.51</v>
+        <v>-3.99</v>
       </c>
       <c r="L29" t="n">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="M29" t="n">
         <v>1.44</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.74</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45369.55208333334</v>
+        <v>45370.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1642</v>
+        <v>1611.35</v>
       </c>
       <c r="I30" t="n">
         <v>1611.392388095324</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>68.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="K30" t="n">
-        <v>10.21</v>
+        <v>8.15</v>
       </c>
       <c r="L30" t="n">
         <v>1.6</v>
@@ -2151,7 +2510,7 @@
         <v>2.25</v>
       </c>
       <c r="N30" t="n">
-        <v>2.08</v>
+        <v>2.86</v>
       </c>
       <c r="O30" t="n">
         <v>1.45</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.55</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1501.9</v>
+        <v>1508.2</v>
       </c>
       <c r="I31" t="n">
         <v>1507.772667926651</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K31" t="n">
-        <v>6.79</v>
+        <v>6.4</v>
       </c>
       <c r="L31" t="n">
         <v>1.87</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>3.46</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45408.55208333334</v>
+        <v>45411.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1477</v>
+        <v>1386.3</v>
       </c>
       <c r="I32" t="n">
         <v>1455.986553759122</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.07</v>
+        <v>-8.08</v>
       </c>
       <c r="L32" t="n">
-        <v>2.87</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>-0</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>1.66</v>
+        <v>6.01</v>
       </c>
       <c r="O32" t="n">
         <v>-1.66</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45448.55208333334</v>
+        <v>45449.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1347.15</v>
+        <v>1389.7</v>
       </c>
       <c r="I33" t="n">
         <v>1353.923269343329</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K33" t="n">
-        <v>2.82</v>
+        <v>-0.25</v>
       </c>
       <c r="L33" t="n">
         <v>3.59</v>
@@ -2322,7 +2717,7 @@
         <v>2.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.06</v>
+        <v>3.63</v>
       </c>
       <c r="O33" t="n">
         <v>-6.01</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>7.13</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1605</v>
+        <v>1559.35</v>
       </c>
       <c r="I34" t="n">
         <v>1586.680187196895</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K34" t="n">
-        <v>15.49</v>
+        <v>12.21</v>
       </c>
       <c r="L34" t="n">
         <v>2.79</v>
       </c>
       <c r="M34" t="n">
-        <v>1.19</v>
+        <v>1.87</v>
       </c>
       <c r="N34" t="n">
-        <v>2.1</v>
+        <v>2.93</v>
       </c>
       <c r="O34" t="n">
         <v>3.63</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>5.16</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1623.35</v>
+        <v>1664.2</v>
       </c>
       <c r="I35" t="n">
         <v>1635.105272262105</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.1</v>
+        <v>-6.72</v>
       </c>
       <c r="L35" t="n">
-        <v>4.51</v>
+        <v>6.81</v>
       </c>
       <c r="M35" t="n">
         <v>1.53</v>
       </c>
       <c r="N35" t="n">
-        <v>1.84</v>
+        <v>2.79</v>
       </c>
       <c r="O35" t="n">
         <v>-2.93</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.42</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1760.1</v>
+        <v>1736.5</v>
       </c>
       <c r="I36" t="n">
         <v>1754.61289570645</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K36" t="n">
-        <v>5.76</v>
+        <v>4.34</v>
       </c>
       <c r="L36" t="n">
         <v>1.89</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>5.57</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45561.55208333334</v>
+        <v>45562.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1782</v>
+        <v>1812.45</v>
       </c>
       <c r="I37" t="n">
         <v>1811.420879126998</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.62</v>
+        <v>-4.37</v>
       </c>
       <c r="L37" t="n">
-        <v>4.14</v>
+        <v>5.3</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9</v>
+        <v>1.57</v>
       </c>
       <c r="N37" t="n">
         <v>1.62</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.64</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45595.55208333334</v>
+        <v>45596.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1853.75</v>
+        <v>1782.1</v>
       </c>
       <c r="I38" t="n">
         <v>1800.251805188586</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K38" t="n">
-        <v>2.28</v>
+        <v>-1.67</v>
       </c>
       <c r="L38" t="n">
         <v>3.83</v>
@@ -2607,7 +3062,7 @@
         <v>2.12</v>
       </c>
       <c r="N38" t="n">
-        <v>2.06</v>
+        <v>4.36</v>
       </c>
       <c r="O38" t="n">
         <v>1.52</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>6.3</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1838</v>
+        <v>1867.25</v>
       </c>
       <c r="I39" t="n">
         <v>1846.272133310556</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.14</v>
+        <v>-4.78</v>
       </c>
       <c r="L39" t="n">
-        <v>4.51</v>
+        <v>5.1</v>
       </c>
       <c r="M39" t="n">
         <v>0.98</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.39</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45649.55208333334</v>
+        <v>45650.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1900.8</v>
+        <v>1896.35</v>
       </c>
       <c r="I40" t="n">
         <v>1896.468906941137</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K40" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="L40" t="n">
         <v>2.8</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>4.89</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45659.38541666666</v>
+        <v>45659.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>1954.05</v>
+        <v>1966.45</v>
       </c>
       <c r="I41" t="n">
         <v>1958.920884591838</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.04</v>
+        <v>-3.7</v>
       </c>
       <c r="L41" t="n">
-        <v>3.83</v>
+        <v>4.22</v>
       </c>
       <c r="M41" t="n">
         <v>0.72</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.35</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45670.55208333334</v>
+        <v>45671.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1975</v>
+        <v>1824.2</v>
       </c>
       <c r="I42" t="n">
         <v>1902.54756885643</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>0.43</v>
+        <v>-7.23</v>
       </c>
       <c r="L42" t="n">
-        <v>3.66</v>
+        <v>8.58</v>
       </c>
       <c r="M42" t="n">
-        <v>0.55</v>
+        <v>1.97</v>
       </c>
       <c r="N42" t="n">
-        <v>1.63</v>
+        <v>7.85</v>
       </c>
       <c r="O42" t="n">
         <v>2.87</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>9.92</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45737.55208333334</v>
+        <v>45740.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1565</v>
+        <v>1595.35</v>
       </c>
       <c r="I43" t="n">
         <v>1594.867965006122</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="K43" t="n">
-        <v>14.21</v>
+        <v>12.55</v>
       </c>
       <c r="L43" t="n">
         <v>6.29</v>
       </c>
       <c r="M43" t="n">
-        <v>0.88</v>
+        <v>1.66</v>
       </c>
       <c r="N43" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="O43" t="n">
         <v>-7.85</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.56</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45748.38541666666</v>
+        <v>45748.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1549</v>
+        <v>1534.5</v>
       </c>
       <c r="I44" t="n">
         <v>1548.236307916662</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.91</v>
+        <v>-3.81</v>
       </c>
       <c r="L44" t="n">
-        <v>3.09</v>
+        <v>4.34</v>
       </c>
       <c r="M44" t="n">
         <v>1.29</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.98</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1439</v>
+        <v>1494.4</v>
       </c>
       <c r="I45" t="n">
         <v>1444.013206675172</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>6.22</v>
+        <v>2.61</v>
       </c>
       <c r="L45" t="n">
         <v>0.98</v>
@@ -3006,7 +3545,7 @@
         <v>1.9</v>
       </c>
       <c r="N45" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="O45" t="n">
         <v>-3.49</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.57</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45847.55208333334</v>
+        <v>45848.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1673</v>
+        <v>1661</v>
       </c>
       <c r="I46" t="n">
         <v>1671.69783278905</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>80</v>
       </c>
       <c r="K46" t="n">
-        <v>11.95</v>
+        <v>11.15</v>
       </c>
       <c r="L46" t="n">
         <v>4.31</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.12</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45880.55208333334</v>
+        <v>45881.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1484.1</v>
+        <v>1501.4</v>
       </c>
       <c r="I47" t="n">
         <v>1499.832841213258</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K47" t="n">
-        <v>10.65</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L47" t="n">
         <v>1.14</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>4.2</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1489.3</v>
+        <v>1451.7</v>
       </c>
       <c r="I48" t="n">
         <v>1452.001744490315</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.31</v>
       </c>
       <c r="L48" t="n">
-        <v>2.89</v>
+        <v>3.42</v>
       </c>
       <c r="M48" t="n">
         <v>0.79</v>
       </c>
       <c r="N48" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="O48" t="n">
         <v>0.9399999999999999</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.23</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1425</v>
+        <v>1470</v>
       </c>
       <c r="I49" t="n">
         <v>1464.218911553276</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K49" t="n">
-        <v>1.84</v>
+        <v>-1.26</v>
       </c>
       <c r="L49" t="n">
         <v>2.5</v>
       </c>
       <c r="M49" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
         <v>-2.63</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.57</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1470.2</v>
+        <v>1440.1</v>
       </c>
       <c r="I50" t="n">
         <v>1445.786529210362</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K50" t="n">
-        <v>0.01</v>
+        <v>-2.03</v>
       </c>
       <c r="L50" t="n">
-        <v>2.58</v>
+        <v>3.74</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1</v>
+        <v>3.21</v>
       </c>
       <c r="N50" t="n">
-        <v>1.45</v>
+        <v>1.92</v>
       </c>
       <c r="O50" t="n">
         <v>2.75</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>3.6</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45937.55208333334</v>
+        <v>45938.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1435.5</v>
+        <v>1453.7</v>
       </c>
       <c r="I51" t="n">
         <v>1437.40318247823</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K51" t="n">
-        <v>0.32</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>0.63</v>
+        <v>1.29</v>
       </c>
       <c r="M51" t="n">
         <v>0.47</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.49</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45986.38541666666</v>
+        <v>45986.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1604.6</v>
+        <v>1598.9</v>
       </c>
       <c r="I52" t="n">
         <v>1601.795090055818</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>10.38</v>
+        <v>9.99</v>
       </c>
       <c r="L52" t="n">
         <v>1.82</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.02</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45995.55208333334</v>
+        <v>45996.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1655.5</v>
+        <v>1685</v>
       </c>
       <c r="I53" t="n">
         <v>1663.178616470473</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.54</v>
+        <v>-5.38</v>
       </c>
       <c r="L53" t="n">
-        <v>4.57</v>
+        <v>5.76</v>
       </c>
       <c r="M53" t="n">
         <v>0.66</v>
       </c>
       <c r="N53" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="O53" t="n">
         <v>-0.8100000000000001</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>4.52</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46020.38541666666</v>
+        <v>46020.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1640</v>
+        <v>1631</v>
       </c>
       <c r="I54" t="n">
         <v>1632.828751103372</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.67</v>
+        <v>-3.2</v>
       </c>
       <c r="L54" t="n">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="M54" t="n">
         <v>0.32</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>3.37</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1643</v>
+        <v>1666.7</v>
       </c>
       <c r="I55" t="n">
         <v>1665.75397618804</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.74</v>
+        <v>-2.19</v>
       </c>
       <c r="L55" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="M55" t="n">
         <v>0.26</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>4.17</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1692.2</v>
+        <v>1609.5</v>
       </c>
       <c r="I56" t="n">
         <v>1657.703124624535</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K56" t="n">
-        <v>1.53</v>
+        <v>-3.43</v>
       </c>
       <c r="L56" t="n">
-        <v>3.22</v>
+        <v>4.84</v>
       </c>
       <c r="M56" t="n">
-        <v>0.88</v>
+        <v>2.97</v>
       </c>
       <c r="N56" t="n">
-        <v>1.7</v>
+        <v>4.47</v>
       </c>
       <c r="O56" t="n">
         <v>1.16</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.26</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46104.55208333334</v>
+        <v>46105.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1357.1</v>
+        <v>1385</v>
       </c>
       <c r="I57" t="n">
         <v>1382.107724566998</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K57" t="n">
-        <v>15.68</v>
+        <v>13.95</v>
       </c>
       <c r="L57" t="n">
         <v>2.21</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.57</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46133.55208333334</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1439</v>
+        <v>1286.2</v>
       </c>
       <c r="I58" t="n">
         <v>1378.950437306143</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>3.9</v>
+        <v>-7.13</v>
       </c>
       <c r="L58" t="n">
-        <v>3.52</v>
+        <v>7.51</v>
       </c>
       <c r="M58" t="n">
-        <v>1.96</v>
+        <v>6.53</v>
       </c>
       <c r="N58" t="n">
-        <v>1.84</v>
+        <v>10.6</v>
       </c>
       <c r="O58" t="n">
         <v>1.32</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>11.17</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46169.55208333334</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1166.9</v>
+        <v>1183.2</v>
       </c>
       <c r="I59" t="n">
         <v>1181.46453124081</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K59" t="n">
-        <v>9.279999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="L59" t="n">
         <v>5.58</v>
       </c>
       <c r="M59" t="n">
-        <v>0.85</v>
+        <v>1.12</v>
       </c>
       <c r="N59" t="n">
         <v>2.95</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>3.82</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46176.38541666666</v>
+        <v>46176.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1183.4</v>
+        <v>1177.3</v>
       </c>
       <c r="I60" t="n">
         <v>1179.080439665937</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>0.02</v>
+        <v>-0.5</v>
       </c>
       <c r="L60" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="M60" t="n">
         <v>1.22</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.25</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46190.38541666666</v>
+        <v>46190.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1162.5</v>
+        <v>1165.2</v>
       </c>
       <c r="I61" t="n">
         <v>1163.322890634107</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="L61" t="n">
         <v>0.6899999999999999</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.63</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46196.38541666666</v>
+        <v>46196.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>1112.5</v>
+        <v>1108.3</v>
       </c>
       <c r="I62" t="n">
         <v>1111.307595028519</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.52</v>
+        <v>-4.88</v>
       </c>
       <c r="L62" t="n">
         <v>6.33</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.8</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1080.5</v>
+        <v>1150.4</v>
       </c>
       <c r="I63" t="n">
         <v>1099.240312063913</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>2.51</v>
+        <v>-3.8</v>
       </c>
       <c r="L63" t="n">
-        <v>2.27</v>
+        <v>4.57</v>
       </c>
       <c r="M63" t="n">
-        <v>1.84</v>
+        <v>4.31</v>
       </c>
       <c r="N63" t="n">
-        <v>4.4</v>
+        <v>5.51</v>
       </c>
       <c r="O63" t="n">
         <v>-1.81</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46251.55208333334</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1328.4</v>
+        <v>1300</v>
       </c>
       <c r="I64" t="n">
         <v>1311.690169632957</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K64" t="n">
-        <v>15.47</v>
+        <v>13</v>
       </c>
       <c r="L64" t="n">
         <v>3.07</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>5.13</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1316.1</v>
+        <v>1362.4</v>
       </c>
       <c r="I65" t="n">
         <v>1338.438887605233</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.24</v>
+        <v>-4.8</v>
       </c>
       <c r="L65" t="n">
-        <v>3.48</v>
+        <v>5.23</v>
       </c>
       <c r="M65" t="n">
         <v>1.48</v>
       </c>
       <c r="N65" t="n">
-        <v>2.35</v>
+        <v>2.74</v>
       </c>
       <c r="O65" t="n">
         <v>-2.51</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>6.63</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46269.55208333334</v>
+        <v>46272.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1293.6</v>
+        <v>1264.5</v>
       </c>
       <c r="I66" t="n">
         <v>1291.388286232187</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>-5.05</v>
+        <v>-7.19</v>
       </c>
       <c r="L66" t="n">
-        <v>5.23</v>
+        <v>7.22</v>
       </c>
       <c r="M66" t="n">
-        <v>0.89</v>
+        <v>1.69</v>
       </c>
       <c r="N66" t="n">
         <v>1.71</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.1</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1212.3</v>
+        <v>1269</v>
       </c>
       <c r="I67" t="n">
         <v>1268.821639205369</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K67" t="n">
-        <v>4.13</v>
+        <v>-0.36</v>
       </c>
       <c r="L67" t="n">
         <v>2.02</v>
       </c>
       <c r="M67" t="n">
-        <v>0.03</v>
+        <v>3.27</v>
       </c>
       <c r="N67" t="n">
-        <v>1.11</v>
+        <v>3.96</v>
       </c>
       <c r="O67" t="n">
         <v>-0.9399999999999999</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.36</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46296.55208333334</v>
+        <v>46300.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1247.5</v>
+        <v>1202.4</v>
       </c>
       <c r="I68" t="n">
         <v>1210.347200173364</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.69</v>
+        <v>-5.25</v>
       </c>
       <c r="L68" t="n">
-        <v>3.48</v>
+        <v>5.59</v>
       </c>
       <c r="M68" t="n">
         <v>0.63</v>
       </c>
       <c r="N68" t="n">
-        <v>2.15</v>
+        <v>3.86</v>
       </c>
       <c r="O68" t="n">
         <v>3.96</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>7.62</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1216</v>
+        <v>1316.6</v>
       </c>
       <c r="I69" t="n">
         <v>1238.287560960058</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.13</v>
+        <v>-9.5</v>
       </c>
       <c r="L69" t="n">
-        <v>3.73</v>
+        <v>9.91</v>
       </c>
       <c r="M69" t="n">
-        <v>0.35</v>
+        <v>2.42</v>
       </c>
       <c r="N69" t="n">
-        <v>2.75</v>
+        <v>8.57</v>
       </c>
       <c r="O69" t="n">
         <v>-3.86</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4434,6 +5273,14 @@
       <c r="Q70" t="n">
         <v>22</v>
       </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6536,7 +7383,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.2</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="6">
@@ -6546,7 +7393,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.1</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="7">
@@ -6556,7 +7403,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>79.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -6566,7 +7413,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6576,7 +7423,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="10">
@@ -6586,7 +7433,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.6</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="11">
@@ -6596,7 +7443,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -6606,7 +7453,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -6616,7 +7463,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67.59999999999999</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="14">
@@ -6626,7 +7473,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.46</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="15">
@@ -6636,7 +7483,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.99</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="16">
@@ -6646,7 +7493,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.93</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="17">
@@ -6656,7 +7503,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.91</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="18">
@@ -6666,7 +7513,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.9</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="19">
@@ -6676,7 +7523,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.97</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="20">
@@ -6686,7 +7533,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.84</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="21">
@@ -6696,7 +7543,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.33</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="22">
@@ -6706,7 +7553,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -6726,7 +7573,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="25">
@@ -6736,7 +7583,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.26</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="26">
@@ -6746,7 +7593,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.36</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="27">
@@ -6756,7 +7603,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.36</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="28">
@@ -6766,7 +7613,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
